--- a/tool_face/Mau_Lich_Dang_Bai_Demo1.xlsx
+++ b/tool_face/Mau_Lich_Dang_Bai_Demo1.xlsx
@@ -1,41 +1,202 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tools\toolfb\tool_face\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8530AFF9-727C-48E8-982D-34F08F2ADEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="MAIN SHEET" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="55">
+  <si>
+    <t>MẪU LỊCH ĐĂNG VIDEO &amp; BÀI VIẾT TỰ ĐỘNG - TOOL_FACE_THINH</t>
+  </si>
+  <si>
+    <t>Video Google Drive - bật chia sẻ Bất kỳ ai có đường liên kết. Schedule: D/M/YYYY_HH:mm. Schedule Comment: số phút sau đăng (VD: 2) hoặc giờ cụ thể.</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Fanpage Channel (Tên | Page ID)</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>Loại Media</t>
+  </si>
+  <si>
+    <t>Media Link</t>
+  </si>
+  <si>
+    <t>Media Thumb</t>
+  </si>
+  <si>
+    <t>Seeding Comment 1</t>
+  </si>
+  <si>
+    <t>Schedule Comment 1</t>
+  </si>
+  <si>
+    <t>Seeding Comment 2</t>
+  </si>
+  <si>
+    <t>Schedule Comment 2</t>
+  </si>
+  <si>
+    <t>Seeding Comment 3</t>
+  </si>
+  <si>
+    <t>Schedule Comment 3</t>
+  </si>
+  <si>
+    <t>Seeding Comment 4</t>
+  </si>
+  <si>
+    <t>Schedule Comment 4</t>
+  </si>
+  <si>
+    <t>Seeding Comment 5</t>
+  </si>
+  <si>
+    <t>Schedule Comment 5</t>
+  </si>
+  <si>
+    <t>Demo1 | 1407700049084608</t>
+  </si>
+  <si>
+    <t>Hé lộ video hậu trường cực kỳ hấp dẫn hôm nay! Mọi người cùng đón xem và để lại cảm nhận bên dưới nhé ❤️</t>
+  </si>
+  <si>
+    <t>9/10/2026_14:00</t>
+  </si>
+  <si>
+    <t>video</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kR4pcsbArDL-BXjRdyVSuxLAywJ6Nq4Q/view?usp=sharing</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Video nét và cuốn hút quá shop ơi, hóng các tập tiếp theo!</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Đoạn này quay ở đâu thế ạ, nhìn chuyên nghiệp ghê!</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>✨ BỘ SƯU TẬP MỚI ĐÃ CHÍNH THỨC CẬP BẾN! Thiết kế tinh tế, phong cách hiện đại giúp bạn tự tin tỏa sáng mỗi ngày. Số lượng có hạn, nhanh tay sở hữu ngay hôm nay!</t>
+  </si>
+  <si>
+    <t>9/10/2026_15:30</t>
+  </si>
+  <si>
+    <t>ảnh</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1523275335684-37898b6baf30?w=800</t>
+  </si>
+  <si>
+    <t>Sản phẩm này còn sẵn hàng không ạ? Cho mình xin giá với!</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Mẫu này đẹp xuất sắc, mình vừa nhận hàng hôm qua đóng gói rất cẩn thận nha.</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>🔥 DEAL ĐỘC QUYỀN CUỐI TUẦN! Giảm ngay 20% cho đơn hàng đầu tiên kèm quà tặng bất ngờ. Đừng bỏ lỡ cơ hội mua sắm thả ga với mức giá ưu đãi nhất!</t>
+  </si>
+  <si>
+    <t>9/10/2026_17:00</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1607082348824-0a96f2a4b9da?w=800</t>
+  </si>
+  <si>
+    <t>Chương trình áp dụng đến ngày nào vậy shop?</t>
+  </si>
+  <si>
+    <t>Đã săn được deal hời, cảm ơn shop nhiều nhé!</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>🌿 3 MẸO HAY BỎ TÚI MỖI NGÀY! Lưu lại ngay những bí quyết đơn giản nhưng cực kỳ hữu ích này để cuộc sống luôn tràn đầy năng lượng và tích cực nhé.</t>
+  </si>
+  <si>
+    <t>9/10/2026_18:30</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1499750310107-5fef28a66643?w=800</t>
+  </si>
+  <si>
+    <t>Bài viết hữu ích quá, cảm ơn trang đã chia sẻ!</t>
+  </si>
+  <si>
+    <t>Mẹo số 2 áp dụng hiệu quả thật sự luôn cả nhà ơi.</t>
+  </si>
+  <si>
+    <t>💌 Gửi lời cảm ơn chân thành đến tất cả quý khách hàng và các bạn đã luôn đồng hành cùng chúng mình trong suốt thời gian qua. Chúc cả nhà một ngày thật nhiều niềm vui và may mắn!</t>
+  </si>
+  <si>
+    <t>9/10/2026_20:00</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1517245386807-bb43f82c33c4?w=800</t>
+  </si>
+  <si>
+    <t>Chúc trang ngày càng phát triển và thành công rực rỡ nhé!</t>
+  </si>
+  <si>
+    <t>now</t>
+  </si>
+  <si>
+    <t>Sẽ luôn ủng hộ shop dài lâu ❤️</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +233,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,340 +565,345 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="32.19921875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>MẪU LỊCH ĐĂNG VIDEO &amp; BÀI VIẾT TỰ ĐỘNG - TOOL_FACE_THINH</v>
+    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Video Google Drive - bật chia sẻ Bất kỳ ai có đường liên kết. Schedule: D/M/YYYY_HH:mm. Schedule Comment: số phút sau đăng (VD: 2) hoặc giờ cụ thể.</v>
+    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>STT</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Fanpage Channel (Tên | Page ID)</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Content</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Schedule</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Loại Media</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Media Link</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Media Thumb</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Seeding Comment 1</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Schedule Comment 1</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Seeding Comment 2</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Schedule Comment 2</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Seeding Comment 3</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Schedule Comment 3</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Seeding Comment 4</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Schedule Comment 4</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Seeding Comment 5</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Schedule Comment 5</v>
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="str">
-        <v>Demo1 | 1407700049084608</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Hé lộ video hậu trường cực kỳ hấp dẫn hôm nay! Mọi người cùng đón xem và để lại cảm nhận bên dưới nhé ❤️</v>
-      </c>
-      <c r="D4" t="str">
-        <v>9/10/2026_14:00</v>
-      </c>
-      <c r="E4" t="str">
-        <v>video</v>
-      </c>
-      <c r="F4" t="str">
-        <v>https://drive.google.com/file/d/1kR4pcsbArDL-BXjRdyVSuxLAywJ6Nq4Q/view?usp=sharing</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v>Video nét và cuốn hút quá shop ơi, hóng các tập tiếp theo!</v>
-      </c>
-      <c r="I4" t="str">
-        <v>2</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Đoạn này quay ở đâu thế ạ, nhìn chuyên nghiệp ghê!</v>
-      </c>
-      <c r="K4" t="str">
-        <v>5</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="str">
-        <v>Demo1 | 1407700049084608</v>
-      </c>
-      <c r="C5" t="str">
-        <v>✨ BỘ SƯU TẬP MỚI ĐÃ CHÍNH THỨC CẬP BẾN! Thiết kế tinh tế, phong cách hiện đại giúp bạn tự tin tỏa sáng mỗi ngày. Số lượng có hạn, nhanh tay sở hữu ngay hôm nay!</v>
-      </c>
-      <c r="D5" t="str">
-        <v>9/10/2026_15:30</v>
-      </c>
-      <c r="E5" t="str">
-        <v>ảnh</v>
-      </c>
-      <c r="F5" t="str">
-        <v>https://images.unsplash.com/photo-1523275335684-37898b6baf30?w=800</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v>Sản phẩm này còn sẵn hàng không ạ? Cho mình xin giá với!</v>
-      </c>
-      <c r="I5" t="str">
-        <v>1</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Mẫu này đẹp xuất sắc, mình vừa nhận hàng hôm qua đóng gói rất cẩn thận nha.</v>
-      </c>
-      <c r="K5" t="str">
-        <v>4</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="str">
-        <v>Demo1 | 1407700049084608</v>
-      </c>
-      <c r="C6" t="str">
-        <v>🔥 DEAL ĐỘC QUYỀN CUỐI TUẦN! Giảm ngay 20% cho đơn hàng đầu tiên kèm quà tặng bất ngờ. Đừng bỏ lỡ cơ hội mua sắm thả ga với mức giá ưu đãi nhất!</v>
-      </c>
-      <c r="D6" t="str">
-        <v>9/10/2026_17:00</v>
-      </c>
-      <c r="E6" t="str">
-        <v>ảnh</v>
-      </c>
-      <c r="F6" t="str">
-        <v>https://images.unsplash.com/photo-1607082348824-0a96f2a4b9da?w=800</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v>Chương trình áp dụng đến ngày nào vậy shop?</v>
-      </c>
-      <c r="I6" t="str">
-        <v>2</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Đã săn được deal hời, cảm ơn shop nhiều nhé!</v>
-      </c>
-      <c r="K6" t="str">
-        <v>6</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="str">
-        <v>Demo1 | 1407700049084608</v>
-      </c>
-      <c r="C7" t="str">
-        <v>🌿 3 MẸO HAY BỎ TÚI MỖI NGÀY! Lưu lại ngay những bí quyết đơn giản nhưng cực kỳ hữu ích này để cuộc sống luôn tràn đầy năng lượng và tích cực nhé.</v>
-      </c>
-      <c r="D7" t="str">
-        <v>9/10/2026_18:30</v>
-      </c>
-      <c r="E7" t="str">
-        <v>ảnh</v>
-      </c>
-      <c r="F7" t="str">
-        <v>https://images.unsplash.com/photo-1499750310107-5fef28a66643?w=800</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v>Bài viết hữu ích quá, cảm ơn trang đã chia sẻ!</v>
-      </c>
-      <c r="I7" t="str">
-        <v>1</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Mẹo số 2 áp dụng hiệu quả thật sự luôn cả nhà ơi.</v>
-      </c>
-      <c r="K7" t="str">
-        <v>5</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="str">
-        <v>Demo1 | 1407700049084608</v>
-      </c>
-      <c r="C8" t="str">
-        <v>💌 Gửi lời cảm ơn chân thành đến tất cả quý khách hàng và các bạn đã luôn đồng hành cùng chúng mình trong suốt thời gian qua. Chúc cả nhà một ngày thật nhiều niềm vui và may mắn!</v>
-      </c>
-      <c r="D8" t="str">
-        <v>9/10/2026_20:00</v>
-      </c>
-      <c r="E8" t="str">
-        <v>ảnh</v>
-      </c>
-      <c r="F8" t="str">
-        <v>https://images.unsplash.com/photo-1517245386807-bb43f82c33c4?w=800</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v>Chúc trang ngày càng phát triển và thành công rực rỡ nhé!</v>
-      </c>
-      <c r="I8" t="str">
-        <v>now</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Sẽ luôn ủng hộ shop dài lâu ❤️</v>
-      </c>
-      <c r="K8" t="str">
-        <v>3</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q8"/>
+    <ignoredError sqref="A1:Q3 A5:A8 A4 C4:Q4 C5:Q8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>